--- a/Scoring Logic and Documentation/method/merec_weights_summary.xlsx
+++ b/Scoring Logic and Documentation/method/merec_weights_summary.xlsx
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -473,19 +473,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.226016</v>
+        <v>0.22831</v>
       </c>
       <c r="E2" t="n">
-        <v>0.078204</v>
+        <v>0.079859</v>
       </c>
       <c r="F2" t="n">
         <v>0.3</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.07398399999999999</v>
+        <v>-0.07169</v>
       </c>
       <c r="H2" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -503,19 +503,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.19825</v>
+        <v>0.205314</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07914599999999999</v>
+        <v>0.070313</v>
       </c>
       <c r="F3" t="n">
         <v>0.35</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.15175</v>
+        <v>-0.144686</v>
       </c>
       <c r="H3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -533,16 +533,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.280942</v>
+        <v>0.281935</v>
       </c>
       <c r="E4" t="n">
-        <v>0.156639</v>
+        <v>0.175805</v>
       </c>
       <c r="F4" t="n">
         <v>0.2</v>
       </c>
       <c r="G4" t="n">
-        <v>0.080942</v>
+        <v>0.08193499999999999</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -563,19 +563,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.294792</v>
+        <v>0.284442</v>
       </c>
       <c r="E5" t="n">
-        <v>0.112875</v>
+        <v>0.124028</v>
       </c>
       <c r="F5" t="n">
         <v>0.15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.144792</v>
+        <v>0.134442</v>
       </c>
       <c r="H5" t="n">
-        <v>72</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.200827</v>
+        <v>0.184696</v>
       </c>
       <c r="E6" t="n">
-        <v>0.084962</v>
+        <v>0.062568</v>
       </c>
       <c r="F6" t="n">
         <v>0.3</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.099173</v>
+        <v>-0.115304</v>
       </c>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.163454</v>
+        <v>0.16058</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06540799999999999</v>
+        <v>0.030637</v>
       </c>
       <c r="F7" t="n">
         <v>0.35</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.186546</v>
+        <v>-0.18942</v>
       </c>
       <c r="H7" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -653,16 +653,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.409751</v>
+        <v>0.46978</v>
       </c>
       <c r="E8" t="n">
-        <v>0.093546</v>
+        <v>0.08612300000000001</v>
       </c>
       <c r="F8" t="n">
         <v>0.2</v>
       </c>
       <c r="G8" t="n">
-        <v>0.209751</v>
+        <v>0.26978</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -683,19 +683,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.225968</v>
+        <v>0.184944</v>
       </c>
       <c r="E9" t="n">
-        <v>0.077318</v>
+        <v>0.066071</v>
       </c>
       <c r="F9" t="n">
         <v>0.15</v>
       </c>
       <c r="G9" t="n">
-        <v>0.07596799999999999</v>
+        <v>0.034944</v>
       </c>
       <c r="H9" t="n">
-        <v>72</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -713,19 +713,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.236298</v>
+        <v>0.250458</v>
       </c>
       <c r="E10" t="n">
-        <v>0.048119</v>
+        <v>0.074865</v>
       </c>
       <c r="F10" t="n">
         <v>0.3</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.06370199999999999</v>
+        <v>-0.049542</v>
       </c>
       <c r="H10" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -743,19 +743,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.264641</v>
+        <v>0.25945</v>
       </c>
       <c r="E11" t="n">
-        <v>0.075021</v>
+        <v>0.079468</v>
       </c>
       <c r="F11" t="n">
         <v>0.35</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.085359</v>
+        <v>-0.09055000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -773,16 +773,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.152757</v>
+        <v>0.161185</v>
       </c>
       <c r="E12" t="n">
-        <v>0.090918</v>
+        <v>0.104816</v>
       </c>
       <c r="F12" t="n">
         <v>0.2</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.047243</v>
+        <v>-0.038815</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.346304</v>
+        <v>0.328907</v>
       </c>
       <c r="E13" t="n">
-        <v>0.103733</v>
+        <v>0.120172</v>
       </c>
       <c r="F13" t="n">
         <v>0.15</v>
       </c>
       <c r="G13" t="n">
-        <v>0.196304</v>
+        <v>0.178907</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -833,16 +833,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.26968</v>
+        <v>0.258463</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07554</v>
+        <v>0.081882</v>
       </c>
       <c r="F14" t="n">
         <v>0.3</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.03032</v>
+        <v>-0.041537</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -863,16 +863,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.182662</v>
+        <v>0.196251</v>
       </c>
       <c r="E15" t="n">
-        <v>0.049491</v>
+        <v>0.046097</v>
       </c>
       <c r="F15" t="n">
         <v>0.35</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.167338</v>
+        <v>-0.153749</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -893,16 +893,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.16762</v>
+        <v>0.184343</v>
       </c>
       <c r="E16" t="n">
-        <v>0.09807299999999999</v>
+        <v>0.111358</v>
       </c>
       <c r="F16" t="n">
         <v>0.2</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.03238</v>
+        <v>-0.015657</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.380038</v>
+        <v>0.360943</v>
       </c>
       <c r="E17" t="n">
-        <v>0.097229</v>
+        <v>0.0994</v>
       </c>
       <c r="F17" t="n">
         <v>0.15</v>
       </c>
       <c r="G17" t="n">
-        <v>0.230038</v>
+        <v>0.210943</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>

--- a/Scoring Logic and Documentation/method/merec_weights_summary.xlsx
+++ b/Scoring Logic and Documentation/method/merec_weights_summary.xlsx
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -473,19 +473,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.22831</v>
+        <v>0.228272</v>
       </c>
       <c r="E2" t="n">
-        <v>0.079859</v>
+        <v>0.080147</v>
       </c>
       <c r="F2" t="n">
         <v>0.3</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.07169</v>
+        <v>-0.071728</v>
       </c>
       <c r="H2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -503,19 +503,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.205314</v>
+        <v>0.205089</v>
       </c>
       <c r="E3" t="n">
-        <v>0.070313</v>
+        <v>0.070517</v>
       </c>
       <c r="F3" t="n">
         <v>0.35</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.144686</v>
+        <v>-0.144911</v>
       </c>
       <c r="H3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -533,16 +533,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.281935</v>
+        <v>0.28362</v>
       </c>
       <c r="E4" t="n">
-        <v>0.175805</v>
+        <v>0.175317</v>
       </c>
       <c r="F4" t="n">
         <v>0.2</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08193499999999999</v>
+        <v>0.08362</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -563,16 +563,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.284442</v>
+        <v>0.28302</v>
       </c>
       <c r="E5" t="n">
-        <v>0.124028</v>
+        <v>0.123339</v>
       </c>
       <c r="F5" t="n">
         <v>0.15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.134442</v>
+        <v>0.13302</v>
       </c>
       <c r="H5" t="n">
         <v>52</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -713,19 +713,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.250458</v>
+        <v>0.25081</v>
       </c>
       <c r="E10" t="n">
-        <v>0.074865</v>
+        <v>0.075609</v>
       </c>
       <c r="F10" t="n">
         <v>0.3</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.049542</v>
+        <v>-0.04919</v>
       </c>
       <c r="H10" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -743,19 +743,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.25945</v>
+        <v>0.259931</v>
       </c>
       <c r="E11" t="n">
-        <v>0.079468</v>
+        <v>0.08022700000000001</v>
       </c>
       <c r="F11" t="n">
         <v>0.35</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.09055000000000001</v>
+        <v>-0.090069</v>
       </c>
       <c r="H11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -773,16 +773,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.161185</v>
+        <v>0.163514</v>
       </c>
       <c r="E12" t="n">
-        <v>0.104816</v>
+        <v>0.104637</v>
       </c>
       <c r="F12" t="n">
         <v>0.2</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.038815</v>
+        <v>-0.036486</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.328907</v>
+        <v>0.325745</v>
       </c>
       <c r="E13" t="n">
-        <v>0.120172</v>
+        <v>0.119374</v>
       </c>
       <c r="F13" t="n">
         <v>0.15</v>
       </c>
       <c r="G13" t="n">
-        <v>0.178907</v>
+        <v>0.175745</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>

--- a/Scoring Logic and Documentation/method/merec_weights_summary.xlsx
+++ b/Scoring Logic and Documentation/method/merec_weights_summary.xlsx
@@ -473,16 +473,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.228272</v>
+        <v>0.164213</v>
       </c>
       <c r="E2" t="n">
-        <v>0.080147</v>
+        <v>0.158337</v>
       </c>
       <c r="F2" t="n">
         <v>0.3</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.071728</v>
+        <v>-0.135787</v>
       </c>
       <c r="H2" t="n">
         <v>44</v>
@@ -503,16 +503,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.205089</v>
+        <v>0.107178</v>
       </c>
       <c r="E3" t="n">
-        <v>0.070517</v>
+        <v>0.114416</v>
       </c>
       <c r="F3" t="n">
         <v>0.35</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.144911</v>
+        <v>-0.242822</v>
       </c>
       <c r="H3" t="n">
         <v>48</v>
@@ -533,16 +533,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.28362</v>
+        <v>0.437285</v>
       </c>
       <c r="E4" t="n">
-        <v>0.175317</v>
+        <v>0.255249</v>
       </c>
       <c r="F4" t="n">
         <v>0.2</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08362</v>
+        <v>0.237285</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -563,16 +563,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.28302</v>
+        <v>0.291324</v>
       </c>
       <c r="E5" t="n">
-        <v>0.123339</v>
+        <v>0.240534</v>
       </c>
       <c r="F5" t="n">
         <v>0.15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.13302</v>
+        <v>0.141324</v>
       </c>
       <c r="H5" t="n">
         <v>52</v>
@@ -593,16 +593,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.184696</v>
+        <v>0.155571</v>
       </c>
       <c r="E6" t="n">
-        <v>0.062568</v>
+        <v>0.144712</v>
       </c>
       <c r="F6" t="n">
         <v>0.3</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.115304</v>
+        <v>-0.144429</v>
       </c>
       <c r="H6" t="n">
         <v>17</v>
@@ -623,16 +623,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.16058</v>
+        <v>0.127537</v>
       </c>
       <c r="E7" t="n">
-        <v>0.030637</v>
+        <v>0.09975100000000001</v>
       </c>
       <c r="F7" t="n">
         <v>0.35</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.18942</v>
+        <v>-0.222463</v>
       </c>
       <c r="H7" t="n">
         <v>17</v>
@@ -653,16 +653,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.46978</v>
+        <v>0.673507</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08612300000000001</v>
+        <v>0.222379</v>
       </c>
       <c r="F8" t="n">
         <v>0.2</v>
       </c>
       <c r="G8" t="n">
-        <v>0.26978</v>
+        <v>0.473507</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -683,16 +683,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.184944</v>
+        <v>0.043385</v>
       </c>
       <c r="E9" t="n">
-        <v>0.066071</v>
+        <v>0.057996</v>
       </c>
       <c r="F9" t="n">
         <v>0.15</v>
       </c>
       <c r="G9" t="n">
-        <v>0.034944</v>
+        <v>-0.106615</v>
       </c>
       <c r="H9" t="n">
         <v>52</v>
@@ -713,16 +713,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.25081</v>
+        <v>0.126796</v>
       </c>
       <c r="E10" t="n">
-        <v>0.075609</v>
+        <v>0.174136</v>
       </c>
       <c r="F10" t="n">
         <v>0.3</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.04919</v>
+        <v>-0.173204</v>
       </c>
       <c r="H10" t="n">
         <v>27</v>
@@ -743,16 +743,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.259931</v>
+        <v>0.056389</v>
       </c>
       <c r="E11" t="n">
-        <v>0.08022700000000001</v>
+        <v>0.137667</v>
       </c>
       <c r="F11" t="n">
         <v>0.35</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.090069</v>
+        <v>-0.293611</v>
       </c>
       <c r="H11" t="n">
         <v>31</v>
@@ -773,16 +773,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.163514</v>
+        <v>0.32746</v>
       </c>
       <c r="E12" t="n">
-        <v>0.104637</v>
+        <v>0.13695</v>
       </c>
       <c r="F12" t="n">
         <v>0.2</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.036486</v>
+        <v>0.12746</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.325745</v>
+        <v>0.489354</v>
       </c>
       <c r="E13" t="n">
-        <v>0.119374</v>
+        <v>0.1771</v>
       </c>
       <c r="F13" t="n">
         <v>0.15</v>
       </c>
       <c r="G13" t="n">
-        <v>0.175745</v>
+        <v>0.339354</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -833,16 +833,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.258463</v>
+        <v>0.222423</v>
       </c>
       <c r="E14" t="n">
-        <v>0.081882</v>
+        <v>0.139298</v>
       </c>
       <c r="F14" t="n">
         <v>0.3</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.041537</v>
+        <v>-0.07757699999999999</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -863,16 +863,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.196251</v>
+        <v>0.143267</v>
       </c>
       <c r="E15" t="n">
-        <v>0.046097</v>
+        <v>0.072005</v>
       </c>
       <c r="F15" t="n">
         <v>0.35</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.153749</v>
+        <v>-0.206733</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -893,16 +893,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.184343</v>
+        <v>0.258223</v>
       </c>
       <c r="E16" t="n">
-        <v>0.111358</v>
+        <v>0.150291</v>
       </c>
       <c r="F16" t="n">
         <v>0.2</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.015657</v>
+        <v>0.058223</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -923,16 +923,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.360943</v>
+        <v>0.376087</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0994</v>
+        <v>0.159695</v>
       </c>
       <c r="F17" t="n">
         <v>0.15</v>
       </c>
       <c r="G17" t="n">
-        <v>0.210943</v>
+        <v>0.226087</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>

--- a/Scoring Logic and Documentation/method/merec_weights_summary.xlsx
+++ b/Scoring Logic and Documentation/method/merec_weights_summary.xlsx
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -473,19 +473,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.164213</v>
+        <v>0.156127</v>
       </c>
       <c r="E2" t="n">
-        <v>0.158337</v>
+        <v>0.149614</v>
       </c>
       <c r="F2" t="n">
         <v>0.3</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.135787</v>
+        <v>-0.143873</v>
       </c>
       <c r="H2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -503,19 +503,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.107178</v>
+        <v>0.106592</v>
       </c>
       <c r="E3" t="n">
-        <v>0.114416</v>
+        <v>0.113787</v>
       </c>
       <c r="F3" t="n">
         <v>0.35</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.242822</v>
+        <v>-0.243408</v>
       </c>
       <c r="H3" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -533,16 +533,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.437285</v>
+        <v>0.430352</v>
       </c>
       <c r="E4" t="n">
-        <v>0.255249</v>
+        <v>0.251176</v>
       </c>
       <c r="F4" t="n">
         <v>0.2</v>
       </c>
       <c r="G4" t="n">
-        <v>0.237285</v>
+        <v>0.230352</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -563,19 +563,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.291324</v>
+        <v>0.306928</v>
       </c>
       <c r="E5" t="n">
-        <v>0.240534</v>
+        <v>0.236064</v>
       </c>
       <c r="F5" t="n">
         <v>0.15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.141324</v>
+        <v>0.156928</v>
       </c>
       <c r="H5" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.155571</v>
+        <v>0.133398</v>
       </c>
       <c r="E6" t="n">
-        <v>0.144712</v>
+        <v>0.116563</v>
       </c>
       <c r="F6" t="n">
         <v>0.3</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.144429</v>
+        <v>-0.166602</v>
       </c>
       <c r="H6" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.127537</v>
+        <v>0.127315</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09975100000000001</v>
+        <v>0.09757299999999999</v>
       </c>
       <c r="F7" t="n">
         <v>0.35</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.222463</v>
+        <v>-0.222685</v>
       </c>
       <c r="H7" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -653,16 +653,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.673507</v>
+        <v>0.667153</v>
       </c>
       <c r="E8" t="n">
-        <v>0.222379</v>
+        <v>0.214804</v>
       </c>
       <c r="F8" t="n">
         <v>0.2</v>
       </c>
       <c r="G8" t="n">
-        <v>0.473507</v>
+        <v>0.467153</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -683,19 +683,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.043385</v>
+        <v>0.072134</v>
       </c>
       <c r="E9" t="n">
-        <v>0.057996</v>
+        <v>0.100329</v>
       </c>
       <c r="F9" t="n">
         <v>0.15</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.106615</v>
+        <v>-0.077866</v>
       </c>
       <c r="H9" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -713,19 +713,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.126796</v>
+        <v>0.126303</v>
       </c>
       <c r="E10" t="n">
-        <v>0.174136</v>
+        <v>0.171759</v>
       </c>
       <c r="F10" t="n">
         <v>0.3</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.173204</v>
+        <v>-0.173697</v>
       </c>
       <c r="H10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -743,19 +743,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.056389</v>
+        <v>0.055458</v>
       </c>
       <c r="E11" t="n">
-        <v>0.137667</v>
+        <v>0.13752</v>
       </c>
       <c r="F11" t="n">
         <v>0.35</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.293611</v>
+        <v>-0.294542</v>
       </c>
       <c r="H11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -773,16 +773,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.32746</v>
+        <v>0.327035</v>
       </c>
       <c r="E12" t="n">
-        <v>0.13695</v>
+        <v>0.137493</v>
       </c>
       <c r="F12" t="n">
         <v>0.2</v>
       </c>
       <c r="G12" t="n">
-        <v>0.12746</v>
+        <v>0.127035</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.489354</v>
+        <v>0.491204</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1771</v>
+        <v>0.175379</v>
       </c>
       <c r="F13" t="n">
         <v>0.15</v>
       </c>
       <c r="G13" t="n">
-        <v>0.339354</v>
+        <v>0.341204</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -833,16 +833,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.222423</v>
+        <v>0.223237</v>
       </c>
       <c r="E14" t="n">
-        <v>0.139298</v>
+        <v>0.13871</v>
       </c>
       <c r="F14" t="n">
         <v>0.3</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.07757699999999999</v>
+        <v>-0.076763</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -863,16 +863,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.143267</v>
+        <v>0.143312</v>
       </c>
       <c r="E15" t="n">
-        <v>0.072005</v>
+        <v>0.071177</v>
       </c>
       <c r="F15" t="n">
         <v>0.35</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.206733</v>
+        <v>-0.206688</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -893,16 +893,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.258223</v>
+        <v>0.248698</v>
       </c>
       <c r="E16" t="n">
-        <v>0.150291</v>
+        <v>0.144613</v>
       </c>
       <c r="F16" t="n">
         <v>0.2</v>
       </c>
       <c r="G16" t="n">
-        <v>0.058223</v>
+        <v>0.048698</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.376087</v>
+        <v>0.384752</v>
       </c>
       <c r="E17" t="n">
-        <v>0.159695</v>
+        <v>0.161699</v>
       </c>
       <c r="F17" t="n">
         <v>0.15</v>
       </c>
       <c r="G17" t="n">
-        <v>0.226087</v>
+        <v>0.234752</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>

--- a/Scoring Logic and Documentation/method/merec_weights_summary.xlsx
+++ b/Scoring Logic and Documentation/method/merec_weights_summary.xlsx
@@ -473,16 +473,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.156127</v>
+        <v>0.19356</v>
       </c>
       <c r="E2" t="n">
-        <v>0.149614</v>
+        <v>0.187962</v>
       </c>
       <c r="F2" t="n">
         <v>0.3</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.143873</v>
+        <v>-0.10644</v>
       </c>
       <c r="H2" t="n">
         <v>40</v>
@@ -503,19 +503,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.106592</v>
+        <v>0.131075</v>
       </c>
       <c r="E3" t="n">
-        <v>0.113787</v>
+        <v>0.137307</v>
       </c>
       <c r="F3" t="n">
         <v>0.35</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.243408</v>
+        <v>-0.218925</v>
       </c>
       <c r="H3" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
@@ -533,16 +533,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.430352</v>
+        <v>0.40357</v>
       </c>
       <c r="E4" t="n">
-        <v>0.251176</v>
+        <v>0.269188</v>
       </c>
       <c r="F4" t="n">
         <v>0.2</v>
       </c>
       <c r="G4" t="n">
-        <v>0.230352</v>
+        <v>0.20357</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -563,19 +563,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.306928</v>
+        <v>0.271796</v>
       </c>
       <c r="E5" t="n">
-        <v>0.236064</v>
+        <v>0.229062</v>
       </c>
       <c r="F5" t="n">
         <v>0.15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.156928</v>
+        <v>0.121796</v>
       </c>
       <c r="H5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.133398</v>
+        <v>0.138244</v>
       </c>
       <c r="E6" t="n">
-        <v>0.116563</v>
+        <v>0.122743</v>
       </c>
       <c r="F6" t="n">
         <v>0.3</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.166602</v>
+        <v>-0.161756</v>
       </c>
       <c r="H6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -623,16 +623,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.127315</v>
+        <v>0.127688</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09757299999999999</v>
+        <v>0.096528</v>
       </c>
       <c r="F7" t="n">
         <v>0.35</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.222685</v>
+        <v>-0.222312</v>
       </c>
       <c r="H7" t="n">
         <v>11</v>
@@ -653,16 +653,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.667153</v>
+        <v>0.662899</v>
       </c>
       <c r="E8" t="n">
-        <v>0.214804</v>
+        <v>0.216022</v>
       </c>
       <c r="F8" t="n">
         <v>0.2</v>
       </c>
       <c r="G8" t="n">
-        <v>0.467153</v>
+        <v>0.462899</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -683,19 +683,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.072134</v>
+        <v>0.071169</v>
       </c>
       <c r="E9" t="n">
-        <v>0.100329</v>
+        <v>0.098147</v>
       </c>
       <c r="F9" t="n">
         <v>0.15</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.077866</v>
+        <v>-0.078831</v>
       </c>
       <c r="H9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10">
@@ -713,16 +713,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.126303</v>
+        <v>0.207971</v>
       </c>
       <c r="E10" t="n">
-        <v>0.171759</v>
+        <v>0.254088</v>
       </c>
       <c r="F10" t="n">
         <v>0.3</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.173697</v>
+        <v>-0.092029</v>
       </c>
       <c r="H10" t="n">
         <v>28</v>
@@ -743,19 +743,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.055458</v>
+        <v>0.043979</v>
       </c>
       <c r="E11" t="n">
-        <v>0.13752</v>
+        <v>0.111779</v>
       </c>
       <c r="F11" t="n">
         <v>0.35</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.294542</v>
+        <v>-0.306021</v>
       </c>
       <c r="H11" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
@@ -773,16 +773,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.327035</v>
+        <v>0.29187</v>
       </c>
       <c r="E12" t="n">
-        <v>0.137493</v>
+        <v>0.149941</v>
       </c>
       <c r="F12" t="n">
         <v>0.2</v>
       </c>
       <c r="G12" t="n">
-        <v>0.127035</v>
+        <v>0.09186999999999999</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.491204</v>
+        <v>0.45618</v>
       </c>
       <c r="E13" t="n">
-        <v>0.175379</v>
+        <v>0.207363</v>
       </c>
       <c r="F13" t="n">
         <v>0.15</v>
       </c>
       <c r="G13" t="n">
-        <v>0.341204</v>
+        <v>0.30618</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -833,19 +833,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.223237</v>
+        <v>0.248147</v>
       </c>
       <c r="E14" t="n">
-        <v>0.13871</v>
+        <v>0.137557</v>
       </c>
       <c r="F14" t="n">
         <v>0.3</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.076763</v>
+        <v>-0.051853</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.143312</v>
+        <v>0.24439</v>
       </c>
       <c r="E15" t="n">
-        <v>0.071177</v>
+        <v>0.13127</v>
       </c>
       <c r="F15" t="n">
         <v>0.35</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.206688</v>
+        <v>-0.10561</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -893,16 +893,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.248698</v>
+        <v>0.202824</v>
       </c>
       <c r="E16" t="n">
-        <v>0.144613</v>
+        <v>0.157804</v>
       </c>
       <c r="F16" t="n">
         <v>0.2</v>
       </c>
       <c r="G16" t="n">
-        <v>0.048698</v>
+        <v>0.002824</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -923,16 +923,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.384752</v>
+        <v>0.304639</v>
       </c>
       <c r="E17" t="n">
-        <v>0.161699</v>
+        <v>0.156306</v>
       </c>
       <c r="F17" t="n">
         <v>0.15</v>
       </c>
       <c r="G17" t="n">
-        <v>0.234752</v>
+        <v>0.154639</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>

--- a/Scoring Logic and Documentation/method/merec_weights_summary.xlsx
+++ b/Scoring Logic and Documentation/method/merec_weights_summary.xlsx
@@ -473,16 +473,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.19356</v>
+        <v>0.194172</v>
       </c>
       <c r="E2" t="n">
-        <v>0.187962</v>
+        <v>0.188203</v>
       </c>
       <c r="F2" t="n">
         <v>0.3</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.10644</v>
+        <v>-0.105828</v>
       </c>
       <c r="H2" t="n">
         <v>40</v>
@@ -503,16 +503,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.131075</v>
+        <v>0.131673</v>
       </c>
       <c r="E3" t="n">
-        <v>0.137307</v>
+        <v>0.137982</v>
       </c>
       <c r="F3" t="n">
         <v>0.35</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.218925</v>
+        <v>-0.218327</v>
       </c>
       <c r="H3" t="n">
         <v>54</v>
@@ -533,16 +533,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.40357</v>
+        <v>0.401912</v>
       </c>
       <c r="E4" t="n">
-        <v>0.269188</v>
+        <v>0.268356</v>
       </c>
       <c r="F4" t="n">
         <v>0.2</v>
       </c>
       <c r="G4" t="n">
-        <v>0.20357</v>
+        <v>0.201912</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -563,16 +563,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.271796</v>
+        <v>0.272243</v>
       </c>
       <c r="E5" t="n">
-        <v>0.229062</v>
+        <v>0.228722</v>
       </c>
       <c r="F5" t="n">
         <v>0.15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.121796</v>
+        <v>0.122243</v>
       </c>
       <c r="H5" t="n">
         <v>47</v>
@@ -833,16 +833,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.248147</v>
+        <v>0.250328</v>
       </c>
       <c r="E14" t="n">
-        <v>0.137557</v>
+        <v>0.137852</v>
       </c>
       <c r="F14" t="n">
         <v>0.3</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.051853</v>
+        <v>-0.049672</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
@@ -863,16 +863,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.24439</v>
+        <v>0.246522</v>
       </c>
       <c r="E15" t="n">
-        <v>0.13127</v>
+        <v>0.131936</v>
       </c>
       <c r="F15" t="n">
         <v>0.35</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.10561</v>
+        <v>-0.103478</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -893,16 +893,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.202824</v>
+        <v>0.196918</v>
       </c>
       <c r="E16" t="n">
-        <v>0.157804</v>
+        <v>0.144461</v>
       </c>
       <c r="F16" t="n">
         <v>0.2</v>
       </c>
       <c r="G16" t="n">
-        <v>0.002824</v>
+        <v>-0.003082</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -923,16 +923,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.304639</v>
+        <v>0.306231</v>
       </c>
       <c r="E17" t="n">
-        <v>0.156306</v>
+        <v>0.154157</v>
       </c>
       <c r="F17" t="n">
         <v>0.15</v>
       </c>
       <c r="G17" t="n">
-        <v>0.154639</v>
+        <v>0.156231</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>

--- a/Scoring Logic and Documentation/method/merec_weights_summary.xlsx
+++ b/Scoring Logic and Documentation/method/merec_weights_summary.xlsx
@@ -473,16 +473,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.194172</v>
+        <v>0.1943</v>
       </c>
       <c r="E2" t="n">
-        <v>0.188203</v>
+        <v>0.189381</v>
       </c>
       <c r="F2" t="n">
         <v>0.3</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.105828</v>
+        <v>-0.1057</v>
       </c>
       <c r="H2" t="n">
         <v>40</v>
@@ -503,16 +503,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.131673</v>
+        <v>0.131354</v>
       </c>
       <c r="E3" t="n">
-        <v>0.137982</v>
+        <v>0.13812</v>
       </c>
       <c r="F3" t="n">
         <v>0.35</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.218327</v>
+        <v>-0.218646</v>
       </c>
       <c r="H3" t="n">
         <v>54</v>
@@ -533,16 +533,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.401912</v>
+        <v>0.403745</v>
       </c>
       <c r="E4" t="n">
-        <v>0.268356</v>
+        <v>0.267504</v>
       </c>
       <c r="F4" t="n">
         <v>0.2</v>
       </c>
       <c r="G4" t="n">
-        <v>0.201912</v>
+        <v>0.203745</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -563,16 +563,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.272243</v>
+        <v>0.2706</v>
       </c>
       <c r="E5" t="n">
-        <v>0.228722</v>
+        <v>0.227334</v>
       </c>
       <c r="F5" t="n">
         <v>0.15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.122243</v>
+        <v>0.1206</v>
       </c>
       <c r="H5" t="n">
         <v>47</v>
@@ -833,16 +833,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.250328</v>
+        <v>0.250786</v>
       </c>
       <c r="E14" t="n">
-        <v>0.137852</v>
+        <v>0.143353</v>
       </c>
       <c r="F14" t="n">
         <v>0.3</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.049672</v>
+        <v>-0.049214</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
@@ -863,16 +863,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.246522</v>
+        <v>0.245387</v>
       </c>
       <c r="E15" t="n">
-        <v>0.131936</v>
+        <v>0.133446</v>
       </c>
       <c r="F15" t="n">
         <v>0.35</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.103478</v>
+        <v>-0.104613</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -893,16 +893,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.196918</v>
+        <v>0.20345</v>
       </c>
       <c r="E16" t="n">
-        <v>0.144461</v>
+        <v>0.148014</v>
       </c>
       <c r="F16" t="n">
         <v>0.2</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.003082</v>
+        <v>0.00345</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -923,16 +923,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.306231</v>
+        <v>0.300377</v>
       </c>
       <c r="E17" t="n">
-        <v>0.154157</v>
+        <v>0.147877</v>
       </c>
       <c r="F17" t="n">
         <v>0.15</v>
       </c>
       <c r="G17" t="n">
-        <v>0.156231</v>
+        <v>0.150377</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
